--- a/STEP1_REVISED/Step5_Final_Experimental_Holdout_Validation.xlsx
+++ b/STEP1_REVISED/Step5_Final_Experimental_Holdout_Validation.xlsx
@@ -496,28 +496,28 @@
         <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>94.11764705882354</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>5.88235294117647</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9992412761360363</v>
+        <v>0.9949181447997554</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008159307440261979</v>
+        <v>0.01642524095020904</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006184869419067564</v>
+        <v>0.01357906231616343</v>
       </c>
       <c r="K2" t="n">
-        <v>1.45683601761296</v>
+        <v>2.769118171975693</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9889304507702699</v>
+        <v>0.9872736893509028</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0995469829666622</v>
+        <v>0.1157454401324335</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07209730070704991</v>
+        <v>0.08651182752368014</v>
       </c>
       <c r="K3" t="n">
-        <v>4.497070053622965</v>
+        <v>3.788920540897504</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -590,22 +590,22 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5.88235294117647</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9877437129855192</v>
+        <v>0.9883245581405847</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01173831593491012</v>
+        <v>0.0106026319035138</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008760980583228333</v>
+        <v>0.008185474354219711</v>
       </c>
       <c r="K4" t="n">
-        <v>3.93134048941068</v>
+        <v>8.463444490555306</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -686,21 +686,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>0.023333333</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>0.846666667</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8525565339359761</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.00588986693597604</v>
+      </c>
       <c r="I2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -715,22 +719,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="F3" t="n">
-        <v>0.916666667</v>
+        <v>0.903333333</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9208243153885171</v>
+        <v>0.8941871233014876</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004157648388517066</v>
+        <v>-0.00914620969851232</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
@@ -748,25 +752,21 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9866666670000001</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9812548695006634</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.005411797499336624</v>
-      </c>
+        <v>0.993333333</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -781,22 +781,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>0.606666667</v>
+        <v>0.413333333</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5845854986851003</v>
+        <v>0.3852428307822398</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0220811683148997</v>
+        <v>-0.02809050221776022</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -814,22 +814,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>0.873333333</v>
+        <v>0.706666667</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8647175506220238</v>
+        <v>0.6904483212093069</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.008615782377976222</v>
+        <v>-0.01621834579069314</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9866666670000001</v>
+        <v>0.766666667</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9844910926508779</v>
+        <v>0.7323201424258879</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.002175574349122189</v>
+        <v>-0.03434652457411203</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>0.043333333</v>
+        <v>0.306666667</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0394019570750633</v>
+        <v>0.2918065384581127</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.003931375924936698</v>
+        <v>-0.01486012854188729</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -913,22 +913,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="F9" t="n">
-        <v>0.86</v>
+        <v>0.796666667</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8646702590253853</v>
+        <v>0.8095848206326297</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004670259025385315</v>
+        <v>0.01291815363262971</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -958,10 +958,10 @@
         <v>0.91</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9232311235112848</v>
+        <v>0.9209415779463459</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01323112351128475</v>
+        <v>0.01094157794634587</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -979,22 +979,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>0.046666667</v>
+        <v>0.24</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04692389301361734</v>
+        <v>0.2133003104049293</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0002572260136173357</v>
+        <v>-0.02669968959507069</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -1012,22 +1012,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F12" t="n">
-        <v>0.786666667</v>
+        <v>0.826666667</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7897072389569375</v>
+        <v>0.8221933065868315</v>
       </c>
       <c r="H12" t="n">
-        <v>0.003040571956937521</v>
+        <v>-0.004473360413168481</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -1045,22 +1045,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>0.956666667</v>
+        <v>0.643333333</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9590703201198684</v>
+        <v>0.6481067739882954</v>
       </c>
       <c r="H13" t="n">
-        <v>0.002403653119868343</v>
+        <v>0.004773440988295463</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
@@ -1078,22 +1078,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
         <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="F14" t="n">
-        <v>0.496666667</v>
+        <v>0.83</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5067848662662509</v>
+        <v>0.8290928268921984</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01011819926625085</v>
+        <v>-0.0009071731078015288</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="F15" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7897162855129773</v>
+        <v>0.8577962504781058</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0002837144870226904</v>
+        <v>0.007796250478105837</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -1144,22 +1144,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="F16" t="n">
-        <v>0.903333333</v>
+        <v>0.316666667</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9073534727821729</v>
+        <v>0.3063171783067324</v>
       </c>
       <c r="H16" t="n">
-        <v>0.004020139782172971</v>
+        <v>-0.01034948869326763</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -1177,22 +1177,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="F17" t="n">
-        <v>0.45</v>
+        <v>0.863333333</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4425755471119286</v>
+        <v>0.8796085551288252</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.00742445288807142</v>
+        <v>0.01627522212882515</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -1210,25 +1210,21 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
         <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.6971352237996813</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.007135223799681345</v>
-      </c>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1243,22 +1239,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>1.44921875</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7522880136377822</v>
+        <v>1.528794962695607</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2477119863622178</v>
+        <v>0.079576212695607</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
@@ -1276,22 +1272,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="F20" t="n">
-        <v>1.52203125</v>
+        <v>1.50375</v>
       </c>
       <c r="G20" t="n">
-        <v>1.506520340015134</v>
+        <v>1.526633566736228</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.01551090998486626</v>
+        <v>0.02288356673622793</v>
       </c>
       <c r="I20" t="b">
         <v>1</v>
@@ -1309,22 +1305,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="F21" t="n">
-        <v>1.589375</v>
+        <v>1.60703125</v>
       </c>
       <c r="G21" t="n">
-        <v>1.623738401828795</v>
+        <v>1.822758838958556</v>
       </c>
       <c r="H21" t="n">
-        <v>0.03436340182879527</v>
+        <v>0.2157275889585559</v>
       </c>
       <c r="I21" t="b">
         <v>1</v>
@@ -1342,22 +1338,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>1.682526433</v>
+        <v>1.385364496</v>
       </c>
       <c r="G22" t="n">
-        <v>1.597239222674139</v>
+        <v>1.334476038656485</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.08528721032586128</v>
+        <v>-0.0508884573435151</v>
       </c>
       <c r="I22" t="b">
         <v>1</v>
@@ -1375,22 +1371,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D23" t="n">
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="F23" t="n">
-        <v>2.098219254</v>
+        <v>1.850862549</v>
       </c>
       <c r="G23" t="n">
-        <v>2.0528932527158</v>
+        <v>1.777380462962752</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.04532600128419961</v>
+        <v>-0.0734820860372476</v>
       </c>
       <c r="I23" t="b">
         <v>1</v>
@@ -1408,22 +1404,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D24" t="n">
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="F24" t="n">
-        <v>2.228992766</v>
+        <v>1.926265999</v>
       </c>
       <c r="G24" t="n">
-        <v>2.231275328801412</v>
+        <v>1.902655813269863</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00228256280141137</v>
+        <v>-0.0236101857301374</v>
       </c>
       <c r="I24" t="b">
         <v>1</v>
@@ -1441,22 +1437,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D25" t="n">
         <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>1.461111111</v>
       </c>
       <c r="G25" t="n">
-        <v>1.09565123432941</v>
+        <v>1.495270051567742</v>
       </c>
       <c r="H25" t="n">
-        <v>0.09565123432941025</v>
+        <v>0.03415894056774182</v>
       </c>
       <c r="I25" t="b">
         <v>1</v>
@@ -1474,22 +1470,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D26" t="n">
         <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="F26" t="n">
-        <v>2.479059829</v>
+        <v>2.400854701</v>
       </c>
       <c r="G26" t="n">
-        <v>2.559402180650787</v>
+        <v>2.483531642048405</v>
       </c>
       <c r="H26" t="n">
-        <v>0.08034235165078663</v>
+        <v>0.08267694104840473</v>
       </c>
       <c r="I26" t="b">
         <v>1</v>
@@ -1519,10 +1515,10 @@
         <v>2.526495726</v>
       </c>
       <c r="G27" t="n">
-        <v>2.575503813402324</v>
+        <v>2.57911609134373</v>
       </c>
       <c r="H27" t="n">
-        <v>0.04900808740232421</v>
+        <v>0.05262036534373049</v>
       </c>
       <c r="I27" t="b">
         <v>1</v>
@@ -1540,22 +1536,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D28" t="n">
         <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>1.710181137</v>
       </c>
       <c r="G28" t="n">
-        <v>1.12689881925892</v>
+        <v>1.610618651536808</v>
       </c>
       <c r="H28" t="n">
-        <v>0.12689881925892</v>
+        <v>-0.09956248546319157</v>
       </c>
       <c r="I28" t="b">
         <v>1</v>
@@ -1573,22 +1569,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D29" t="n">
         <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F29" t="n">
-        <v>3.026858214</v>
+        <v>3.090568395</v>
       </c>
       <c r="G29" t="n">
-        <v>3.009460045070795</v>
+        <v>3.072045986687107</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.01739816892920487</v>
+        <v>-0.0185224083128932</v>
       </c>
       <c r="I29" t="b">
         <v>1</v>
@@ -1606,22 +1602,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E30" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>3.286071205</v>
+        <v>3.179091688</v>
       </c>
       <c r="G30" t="n">
-        <v>3.24567248275369</v>
+        <v>3.204690415163836</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.04039872224631003</v>
+        <v>0.02559872716383627</v>
       </c>
       <c r="I30" t="b">
         <v>1</v>
@@ -1639,22 +1635,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
         <v>14</v>
       </c>
       <c r="E31" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="F31" t="n">
-        <v>2.65638389</v>
+        <v>3.600685518</v>
       </c>
       <c r="G31" t="n">
-        <v>2.622679896518527</v>
+        <v>3.658969439985555</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.03370399348147313</v>
+        <v>0.05828392198555532</v>
       </c>
       <c r="I31" t="b">
         <v>1</v>
@@ -1672,22 +1668,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D32" t="n">
         <v>14</v>
       </c>
       <c r="E32" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="F32" t="n">
-        <v>3.525278492</v>
+        <v>3.618680377</v>
       </c>
       <c r="G32" t="n">
-        <v>3.579706385985428</v>
+        <v>3.695405003198265</v>
       </c>
       <c r="H32" t="n">
-        <v>0.05442789398542835</v>
+        <v>0.07672462619826481</v>
       </c>
       <c r="I32" t="b">
         <v>1</v>
@@ -1705,22 +1701,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E33" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="F33" t="n">
-        <v>3.77377892</v>
+        <v>2.622767857</v>
       </c>
       <c r="G33" t="n">
-        <v>3.774031596595468</v>
+        <v>2.365304014835883</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0002526765954682375</v>
+        <v>-0.2574638421641171</v>
       </c>
       <c r="I33" t="b">
         <v>1</v>
@@ -1738,22 +1734,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
         <v>16</v>
       </c>
       <c r="E34" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="F34" t="n">
-        <v>3.094866071</v>
+        <v>4.3046875</v>
       </c>
       <c r="G34" t="n">
-        <v>2.868624763228428</v>
+        <v>4.344883005500296</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2262413077715721</v>
+        <v>0.0401955055002956</v>
       </c>
       <c r="I34" t="b">
         <v>1</v>
@@ -1771,22 +1767,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D35" t="n">
         <v>16</v>
       </c>
       <c r="E35" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="F35" t="n">
-        <v>3.943080357</v>
+        <v>4.681919643</v>
       </c>
       <c r="G35" t="n">
-        <v>4.013929140781599</v>
+        <v>4.423194436346759</v>
       </c>
       <c r="H35" t="n">
-        <v>0.07084878378159898</v>
+        <v>-0.2587252066532404</v>
       </c>
       <c r="I35" t="b">
         <v>1</v>
@@ -1804,22 +1800,22 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D36" t="n">
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.129812368</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.03329454901508362</v>
+        <v>0.1394920783556689</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.03329454901508362</v>
+        <v>0.009679710355668919</v>
       </c>
       <c r="I36" t="b">
         <v>1</v>
@@ -1837,22 +1833,22 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D37" t="n">
         <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="F37" t="n">
-        <v>0.155513347</v>
+        <v>0.149682126</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1667982785125635</v>
+        <v>0.1604931609355467</v>
       </c>
       <c r="H37" t="n">
-        <v>0.01128493151256346</v>
+        <v>0.01081103493554669</v>
       </c>
       <c r="I37" t="b">
         <v>1</v>
@@ -1870,22 +1866,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D38" t="n">
         <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="F38" t="n">
-        <v>0.180976271</v>
+        <v>0.185595806</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1759598333787052</v>
+        <v>0.1846307322571314</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.00501643762129475</v>
+        <v>-0.0009650737428685552</v>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -1903,22 +1899,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D39" t="n">
         <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F39" t="n">
-        <v>0.12191595</v>
+        <v>0.056957217</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1027490811059167</v>
+        <v>0.0628784146130543</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.01916686889408334</v>
+        <v>0.005921197613054298</v>
       </c>
       <c r="I39" t="b">
         <v>1</v>
@@ -1936,22 +1932,22 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D40" t="n">
         <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="F40" t="n">
-        <v>0.226452432</v>
+        <v>0.160936952</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2197664400116286</v>
+        <v>0.1407397283889588</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.006685991988371415</v>
+        <v>-0.02019722361104118</v>
       </c>
       <c r="I40" t="b">
         <v>1</v>
@@ -1969,22 +1965,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D41" t="n">
         <v>8</v>
       </c>
       <c r="E41" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="F41" t="n">
-        <v>0.269507547</v>
+        <v>0.182634575</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2579142148047501</v>
+        <v>0.1683021023044128</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.01159333219524988</v>
+        <v>-0.01433247269558716</v>
       </c>
       <c r="I41" t="b">
         <v>1</v>
@@ -2002,22 +1998,22 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D42" t="n">
         <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>0.047106137</v>
       </c>
       <c r="G42" t="n">
-        <v>0.01005288010443478</v>
+        <v>0.07148426095306321</v>
       </c>
       <c r="H42" t="n">
-        <v>0.01005288010443478</v>
+        <v>0.02437812395306321</v>
       </c>
       <c r="I42" t="b">
         <v>1</v>
@@ -2035,22 +2031,22 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D43" t="n">
         <v>10</v>
       </c>
       <c r="E43" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="F43" t="n">
-        <v>0.249815332</v>
+        <v>0.226319718</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2605642008276675</v>
+        <v>0.232013548761956</v>
       </c>
       <c r="H43" t="n">
-        <v>0.01074886882766751</v>
+        <v>0.005693830761955981</v>
       </c>
       <c r="I43" t="b">
         <v>1</v>
@@ -2080,10 +2076,10 @@
         <v>0.267696194</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2779189680215666</v>
+        <v>0.2774301832161995</v>
       </c>
       <c r="H44" t="n">
-        <v>0.01022277402156663</v>
+        <v>0.009733989216199501</v>
       </c>
       <c r="I44" t="b">
         <v>1</v>
@@ -2101,22 +2097,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D45" t="n">
         <v>12</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>0.049264635</v>
       </c>
       <c r="G45" t="n">
-        <v>0.001291001190873959</v>
+        <v>0.06449612401287035</v>
       </c>
       <c r="H45" t="n">
-        <v>0.001291001190873959</v>
+        <v>0.01523148901287034</v>
       </c>
       <c r="I45" t="b">
         <v>1</v>
@@ -2134,22 +2130,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D46" t="n">
         <v>12</v>
       </c>
       <c r="E46" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F46" t="n">
-        <v>0.260389238</v>
+        <v>0.276412389</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2592092589792414</v>
+        <v>0.2730758271227815</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.00117997902075867</v>
+        <v>-0.00333656187721848</v>
       </c>
       <c r="I46" t="b">
         <v>1</v>
@@ -2167,22 +2163,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D47" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E47" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="F47" t="n">
-        <v>0.328983913</v>
+        <v>0.219689143</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3305368444637373</v>
+        <v>0.216838186207731</v>
       </c>
       <c r="H47" t="n">
-        <v>0.001552931463737306</v>
+        <v>-0.002850956792269044</v>
       </c>
       <c r="I47" t="b">
         <v>1</v>
@@ -2200,22 +2196,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D48" t="n">
         <v>14</v>
       </c>
       <c r="E48" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="F48" t="n">
-        <v>0.154289085</v>
+        <v>0.298662612</v>
       </c>
       <c r="G48" t="n">
-        <v>0.148986179549073</v>
+        <v>0.2930033917528271</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.005302905450926959</v>
+        <v>-0.005659220247172858</v>
       </c>
       <c r="I48" t="b">
         <v>1</v>
@@ -2233,22 +2229,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D49" t="n">
         <v>14</v>
       </c>
       <c r="E49" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="F49" t="n">
-        <v>0.281931145</v>
+        <v>0.306444136</v>
       </c>
       <c r="G49" t="n">
-        <v>0.278722065458306</v>
+        <v>0.3059109772332567</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.003209079541694027</v>
+        <v>-0.000533158766743258</v>
       </c>
       <c r="I49" t="b">
         <v>1</v>
@@ -2266,22 +2262,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E50" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="F50" t="n">
-        <v>0.330783285</v>
+        <v>0.09732608700000001</v>
       </c>
       <c r="G50" t="n">
-        <v>0.332123367912947</v>
+        <v>0.09967786540793341</v>
       </c>
       <c r="H50" t="n">
-        <v>0.001340082912947016</v>
+        <v>0.002351778407933408</v>
       </c>
       <c r="I50" t="b">
         <v>1</v>
@@ -2299,22 +2295,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D51" t="n">
         <v>16</v>
       </c>
       <c r="E51" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="F51" t="n">
-        <v>0.151308161</v>
+        <v>0.329237345</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1462528550564679</v>
+        <v>0.3304624708811604</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.005055305943532068</v>
+        <v>0.001225125881160416</v>
       </c>
       <c r="I51" t="b">
         <v>1</v>
@@ -2332,22 +2328,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D52" t="n">
         <v>16</v>
       </c>
       <c r="E52" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="F52" t="n">
-        <v>0.255832691</v>
+        <v>0.367215621</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2677714412100963</v>
+        <v>0.3609635048486182</v>
       </c>
       <c r="H52" t="n">
-        <v>0.01193875021009627</v>
+        <v>-0.00625211615138177</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
@@ -2401,162 +2397,162 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B2" t="n">
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0.023333333</v>
+        <v>0.846666667</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>1.44921875</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.129812368</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="D3" t="n">
-        <v>0.916666667</v>
+        <v>0.903333333</v>
       </c>
       <c r="E3" t="n">
-        <v>1.52203125</v>
+        <v>1.50375</v>
       </c>
       <c r="F3" t="n">
-        <v>0.155513347</v>
+        <v>0.149682126</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B4" t="n">
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9866666670000001</v>
+        <v>0.993333333</v>
       </c>
       <c r="E4" t="n">
-        <v>1.589375</v>
+        <v>1.60703125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.180976271</v>
+        <v>0.185595806</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5" t="n">
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>0.606666667</v>
+        <v>0.413333333</v>
       </c>
       <c r="E5" t="n">
-        <v>1.682526433</v>
+        <v>1.385364496</v>
       </c>
       <c r="F5" t="n">
-        <v>0.12191595</v>
+        <v>0.056957217</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B6" t="n">
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>0.873333333</v>
+        <v>0.706666667</v>
       </c>
       <c r="E6" t="n">
-        <v>2.098219254</v>
+        <v>1.850862549</v>
       </c>
       <c r="F6" t="n">
-        <v>0.226452432</v>
+        <v>0.160936952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B7" t="n">
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9866666670000001</v>
+        <v>0.766666667</v>
       </c>
       <c r="E7" t="n">
-        <v>2.228992766</v>
+        <v>1.926265999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.269507547</v>
+        <v>0.182634575</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" t="n">
         <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>0.043333333</v>
+        <v>0.306666667</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>1.461111111</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.047106137</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9" t="n">
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D9" t="n">
-        <v>0.86</v>
+        <v>0.796666667</v>
       </c>
       <c r="E9" t="n">
-        <v>2.479059829</v>
+        <v>2.400854701</v>
       </c>
       <c r="F9" t="n">
-        <v>0.249815332</v>
+        <v>0.226319718</v>
       </c>
     </row>
     <row r="10">
@@ -2581,162 +2577,162 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" t="n">
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>0.046666667</v>
+        <v>0.24</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>1.710181137</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.049264635</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" t="n">
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>0.786666667</v>
+        <v>0.826666667</v>
       </c>
       <c r="E12" t="n">
-        <v>3.026858214</v>
+        <v>3.090568395</v>
       </c>
       <c r="F12" t="n">
-        <v>0.260389238</v>
+        <v>0.276412389</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>0.956666667</v>
+        <v>0.643333333</v>
       </c>
       <c r="E13" t="n">
-        <v>3.286071205</v>
+        <v>3.179091688</v>
       </c>
       <c r="F13" t="n">
-        <v>0.328983913</v>
+        <v>0.219689143</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>0.496666667</v>
+        <v>0.83</v>
       </c>
       <c r="E14" t="n">
-        <v>2.65638389</v>
+        <v>3.600685518</v>
       </c>
       <c r="F14" t="n">
-        <v>0.154289085</v>
+        <v>0.298662612</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="D15" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="E15" t="n">
-        <v>3.525278492</v>
+        <v>3.618680377</v>
       </c>
       <c r="F15" t="n">
-        <v>0.281931145</v>
+        <v>0.306444136</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>0.903333333</v>
+        <v>0.316666667</v>
       </c>
       <c r="E16" t="n">
-        <v>3.77377892</v>
+        <v>2.622767857</v>
       </c>
       <c r="F16" t="n">
-        <v>0.330783285</v>
+        <v>0.09732608700000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B17" t="n">
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="D17" t="n">
-        <v>0.45</v>
+        <v>0.863333333</v>
       </c>
       <c r="E17" t="n">
-        <v>3.094866071</v>
+        <v>4.3046875</v>
       </c>
       <c r="F17" t="n">
-        <v>0.151308161</v>
+        <v>0.329237345</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B18" t="n">
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>3.943080357</v>
+        <v>4.681919643</v>
       </c>
       <c r="F18" t="n">
-        <v>0.255832691</v>
+        <v>0.367215621</v>
       </c>
     </row>
   </sheetData>
